--- a/胎壓偵測/CITROEN_Data.xlsx
+++ b/胎壓偵測/CITROEN_Data.xlsx
@@ -31399,10 +31399,26 @@
           <t>AUX</t>
         </is>
       </c>
-      <c r="G784" t="inlineStr"/>
-      <c r="H784" t="inlineStr"/>
-      <c r="I784" t="inlineStr"/>
-      <c r="J784" t="inlineStr"/>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>02/2014 -</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>HS 3002 |  &lt; 3.6 Bar Reifendruck</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>SCHRADER</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
